--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484537_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484537_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9675</v>
+        <v>8.693300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5444</v>
+        <v>8.0968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4231</v>
+        <v>0.5965</v>
       </c>
       <c r="G2" t="n">
         <v>2.9569</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5888</v>
+        <v>0.1371</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5052</v>
+        <v>0.0472</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0835</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>4.1333</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.865</v>
+        <v>7.6902</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1256</v>
+        <v>7.5792</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2606</v>
+        <v>0.111</v>
       </c>
       <c r="G3" t="n">
         <v>4.6995</v>
@@ -688,13 +688,13 @@
         <v>2.3823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8895</v>
+        <v>-0.0643</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4419</v>
+        <v>0.0117</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4476</v>
+        <v>-0.076</v>
       </c>
       <c r="V3" t="n">
         <v>1.5889</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6074</v>
+        <v>1.5986</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3688</v>
+        <v>1.6573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2386</v>
+        <v>-0.0587</v>
       </c>
       <c r="G5" t="n">
         <v>1.7311</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0504</v>
+        <v>-0.0592</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0369</v>
+        <v>0.2515</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0134</v>
+        <v>-0.3107</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6231</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8639</v>
+        <v>0.4433</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9656</v>
+        <v>-1.089</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8295</v>
+        <v>1.5322</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8159999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>2.7489</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3787</v>
+        <v>0.9581</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5475</v>
+        <v>0.4242</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8312</v>
+        <v>0.5339</v>
       </c>
       <c r="V7" t="n">
         <v>0.3011</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6513</v>
+        <v>-0.4739</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9965000000000001</v>
+        <v>-0.4881</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6479</v>
+        <v>0.0142</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7438</v>
+        <v>-2.3756</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0642</v>
+        <v>-2.2089</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3204</v>
+        <v>-0.1667</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2568</v>
+        <v>-0.3361</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0903</v>
+        <v>-1.1954</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8335</v>
+        <v>0.8592</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.487</v>
+        <v>-2.0395</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9739</v>
+        <v>-1.0136</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5131</v>
+        <v>-1.0259</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0033</v>
+        <v>-0.0042</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1592</v>
+        <v>-0.152</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1558</v>
+        <v>0.1478</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2774</v>
+        <v>0.6231</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2878</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>A. VIVES HURTADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8284</v>
+        <v>-1.0901</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9417</v>
+        <v>-0.8289</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1132</v>
+        <v>-0.2611</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3756</v>
+        <v>0.3676</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2089</v>
+        <v>1.0312</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1667</v>
+        <v>-0.6636</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3361</v>
+        <v>1.7264</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1954</v>
+        <v>1.4923</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8592</v>
+        <v>0.2341</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0395</v>
+        <v>-1.3588</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0136</v>
+        <v>-0.4611</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0259</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2828</v>
+        <v>-0.733</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3587</v>
+        <v>0.8435</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6056</v>
+        <v>0.1727</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2469</v>
+        <v>0.6708</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6231</v>
+        <v>-1.5681</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6231</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VIVES HURTADO</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1117</v>
+        <v>-1.3291</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2965</v>
+        <v>0.1613</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1848</v>
+        <v>-1.4903</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3676</v>
+        <v>-0.8517</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0312</v>
+        <v>-0.1756</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6636</v>
+        <v>-0.676</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7264</v>
+        <v>1.6903</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4923</v>
+        <v>2.0775</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2341</v>
+        <v>-0.3872</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3588</v>
+        <v>-2.5419</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4611</v>
+        <v>-2.2531</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.2888</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0158</v>
+        <v>3.4819</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8219</v>
+        <v>0.4072</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2949</v>
+        <v>0.3036</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1167</v>
+        <v>0.1037</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5681</v>
+        <v>-2.5339</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8437</v>
+        <v>-2.0826</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0065</v>
+        <v>-0.3357</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8372</v>
+        <v>-1.7469</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8517</v>
+        <v>-1.7438</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1756</v>
+        <v>-2.0642</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.676</v>
+        <v>0.3204</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6903</v>
+        <v>-0.2568</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0775</v>
+        <v>-1.0903</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3872</v>
+        <v>0.8335</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5419</v>
+        <v>-1.487</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2531</v>
+        <v>-0.9739</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2888</v>
+        <v>-0.5131</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>3.4819</v>
+        <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1074</v>
+        <v>0.572</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8642</v>
+        <v>0.8269</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2432</v>
+        <v>-0.2549</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5339</v>
+        <v>-1.2774</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5339</v>
+        <v>-1.2878</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5176</v>
+        <v>-3.7888</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8903</v>
+        <v>-2.5083</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6273</v>
+        <v>-1.2805</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0247</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7244</v>
+        <v>0.4532</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3907</v>
+        <v>0.7726</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6662</v>
+        <v>-0.3194</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3011</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>J. CLIMENT GOMIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0241</v>
+        <v>-5.9287</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.439</v>
+        <v>-4.434</v>
       </c>
       <c r="F13" t="n">
-        <v>0.415</v>
+        <v>-1.4947</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.0074</v>
+        <v>-1.3537</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.3087</v>
+        <v>-1.2608</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3013</v>
+        <v>-0.0929</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6839</v>
+        <v>-0.1401</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9854</v>
+        <v>-0.2075</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3016</v>
+        <v>0.0674</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3235</v>
+        <v>-1.2136</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3232</v>
+        <v>-1.0532</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0003</v>
+        <v>-0.1603</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.2149</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.414</v>
+        <v>-3.6651</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1991</v>
+        <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9105</v>
+        <v>0.0639</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3711</v>
+        <v>-0.0056</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5394</v>
+        <v>0.0696</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2878</v>
+        <v>-1.89</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2878</v>
+        <v>-0.6231</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CLIMENT GOMIS</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.9068</v>
+        <v>-5.9359</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.3378</v>
+        <v>-6.2765</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.569</v>
+        <v>0.3406</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3537</v>
+        <v>-4.0074</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2608</v>
+        <v>-4.3087</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0929</v>
+        <v>0.3013</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1401</v>
+        <v>-1.6839</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2075</v>
+        <v>-1.9854</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0674</v>
+        <v>0.3016</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2136</v>
+        <v>-2.3235</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0532</v>
+        <v>-2.3232</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1603</v>
+        <v>-0.0003</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7489</v>
+        <v>-4.2149</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.6651</v>
+        <v>-6.414</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0858</v>
+        <v>0.9987</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0905</v>
+        <v>0.5336</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0048</v>
+        <v>0.4651</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.89</v>
+        <v>1.2878</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6231</v>
+        <v>1.2878</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,28 +1579,28 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2211000000000016</v>
+        <v>1.597199999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>3.958800000000005</v>
+        <v>5.334999999999996</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.7378</v>
+        <v>-3.737699999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6169000000000002</v>
+        <v>-0.6168999999999993</v>
       </c>
       <c r="H15" t="n">
         <v>-8.471399999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>7.854599999999999</v>
+        <v>7.8546</v>
       </c>
       <c r="J15" t="n">
         <v>18.8786</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2519</v>
+        <v>5.251900000000001</v>
       </c>
       <c r="L15" t="n">
         <v>13.6266</v>
@@ -1624,19 +1624,19 @@
         <v>21.9909</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9298</v>
+        <v>4.306</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8103</v>
+        <v>3.1864</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1197</v>
+        <v>1.1198</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2594000000000003</v>
       </c>
       <c r="W15" t="n">
-        <v>7.0931</v>
+        <v>7.093099999999999</v>
       </c>
       <c r="X15" t="n">
         <v>-7.352699999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3023</v>
+        <v>7.5391</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2079</v>
+        <v>5.3618</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0943</v>
+        <v>2.1773</v>
       </c>
       <c r="G16" t="n">
         <v>2.6125</v>
@@ -1702,13 +1702,13 @@
         <v>3.8484</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5613</v>
+        <v>-0.3245</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4683</v>
+        <v>-0.3144</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.093</v>
+        <v>-0.01</v>
       </c>
       <c r="V16" t="n">
         <v>5.0679</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3204</v>
+        <v>2.7079</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6667</v>
+        <v>1.9552</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.7528</v>
       </c>
       <c r="G17" t="n">
         <v>3.7566</v>
@@ -1780,13 +1780,13 @@
         <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7032</v>
+        <v>-0.3156</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6606</v>
+        <v>-0.3722</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0426</v>
+        <v>0.0565</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2748</v>
+        <v>1.7649</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4093</v>
+        <v>1.5439</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1345</v>
+        <v>0.221</v>
       </c>
       <c r="G18" t="n">
         <v>3.5446</v>
@@ -1858,13 +1858,13 @@
         <v>3.2986</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9084</v>
+        <v>0.3986</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2791</v>
+        <v>0.4137</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3706</v>
+        <v>-0.0151</v>
       </c>
       <c r="V18" t="n">
         <v>0.0208</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3251</v>
+        <v>0.5213</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3251</v>
+        <v>1.5979</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.0766</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3251</v>
+        <v>0.4934</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3251</v>
+        <v>1.8945</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.401</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3251</v>
+        <v>1.7073</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3251</v>
+        <v>2.3067</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.5994</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.2139</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.4122</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.5273</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1485</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.3788</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2774</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.2328</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.3251</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5979</v>
+        <v>0.3251</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5269</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4934</v>
+        <v>0.3251</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8945</v>
+        <v>0.3251</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.401</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7073</v>
+        <v>0.3251</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3067</v>
+        <v>0.3251</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2139</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4122</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8017</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7489</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9776</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1485</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.829</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2774</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3979</v>
+        <v>-0.1846</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7923</v>
+        <v>2.3972</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3944</v>
+        <v>-2.5818</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9125</v>
+        <v>0.8227</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2006</v>
+        <v>-0.0235</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7119</v>
+        <v>0.8462</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3519</v>
+        <v>2.5081</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1018</v>
+        <v>0.5077</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>2.0004</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2644</v>
+        <v>-1.6854</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3024</v>
+        <v>-0.5312</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.962</v>
+        <v>-1.1541</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2986</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>0.902</v>
+        <v>-0.1514</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1441</v>
+        <v>-0.1108</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7579</v>
+        <v>-0.0405</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0208</v>
+        <v>-1.5889</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6022999999999999</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.707</v>
+        <v>-0.5118</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0286</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6784</v>
+        <v>-0.5793</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0476</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3925</v>
+        <v>-0.1972</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4404</v>
+        <v>-0.3443</v>
       </c>
       <c r="U22" t="n">
-        <v>0.048</v>
+        <v>0.1471</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8708</v>
+        <v>-1.0376</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0126</v>
+        <v>-3.7923</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8834</v>
+        <v>2.7546</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8227</v>
+        <v>-0.9125</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0235</v>
+        <v>-0.2006</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8462</v>
+        <v>-0.7119</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5081</v>
+        <v>0.3519</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5077</v>
+        <v>0.1018</v>
       </c>
       <c r="L23" t="n">
-        <v>2.0004</v>
+        <v>0.25</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6854</v>
+        <v>-1.2644</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5312</v>
+        <v>-0.3024</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1541</v>
+        <v>-0.962</v>
       </c>
       <c r="P23" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R23" t="n">
-        <v>0.733</v>
+        <v>3.2986</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8376</v>
+        <v>0.2622</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4955</v>
+        <v>0.1441</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3422</v>
+        <v>0.1182</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5889</v>
+        <v>-0.0208</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5889</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.623</v>
+        <v>-1.4365</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0577</v>
+        <v>1.4423</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6807</v>
+        <v>-2.8789</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7067</v>
@@ -2326,13 +2326,13 @@
         <v>2.5656</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8825</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8627</v>
+        <v>-0.4781</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0198</v>
+        <v>-0.218</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5993</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4076</v>
+        <v>-3.2525</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3841</v>
+        <v>-4.6342</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9766</v>
+        <v>1.3816</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9275</v>
@@ -2404,13 +2404,13 @@
         <v>3.6651</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4362</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8469</v>
+        <v>0.5969</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4107</v>
+        <v>-0.0057</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5082</v>
+        <v>-5.3741</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3345</v>
+        <v>-2.5268</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1737</v>
+        <v>-2.8473</v>
       </c>
       <c r="G26" t="n">
         <v>-4.3436</v>
@@ -2482,13 +2482,13 @@
         <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8219</v>
+        <v>-0.6878</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3137</v>
+        <v>-0.506</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5082</v>
+        <v>-0.1818</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3428</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2209000000000003</v>
+        <v>1.061200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>3.737700000000002</v>
+        <v>3.7377</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.9586</v>
+        <v>-2.6766</v>
       </c>
       <c r="G27" t="n">
         <v>0.6169999999999991</v>
@@ -2533,7 +2533,7 @@
         <v>-7.8544</v>
       </c>
       <c r="J27" t="n">
-        <v>19.49560000000001</v>
+        <v>19.4956</v>
       </c>
       <c r="K27" t="n">
         <v>13.7233</v>
@@ -2545,7 +2545,7 @@
         <v>-18.8786</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.251900000000001</v>
+        <v>-5.2519</v>
       </c>
       <c r="O27" t="n">
         <v>-13.6267</v>
@@ -2560,13 +2560,13 @@
         <v>23.8233</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.93</v>
+        <v>-1.6479</v>
       </c>
       <c r="T27" t="n">
         <v>-1.1196</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8102</v>
+        <v>-0.5281</v>
       </c>
       <c r="V27" t="n">
         <v>0.2595000000000001</v>
